--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130188532</v>
       </c>
       <c r="B2" t="n">
-        <v>92921</v>
+        <v>92923</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130188532</v>
       </c>
       <c r="B2" t="n">
-        <v>92923</v>
+        <v>93010</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130188532</v>
       </c>
       <c r="B2" t="n">
-        <v>93010</v>
+        <v>93013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130188532</v>
       </c>
       <c r="B2" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130188532</v>
       </c>
       <c r="B2" t="n">
-        <v>93039</v>
+        <v>93040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130188532</v>
       </c>
       <c r="B2" t="n">
-        <v>93040</v>
+        <v>93041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130188532</v>
       </c>
       <c r="B2" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130188532</v>
       </c>
       <c r="B2" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23087-2025 artfynd.xlsx
+++ b/artfynd/A 23087-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130188532</v>
+        <v>130189264</v>
       </c>
       <c r="B2" t="n">
-        <v>93047</v>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505194</v>
+        <v>505170</v>
       </c>
       <c r="R2" t="n">
-        <v>6664573</v>
+        <v>6664585</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,6 +769,200 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130188532</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>505194</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6664573</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130188803</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>505170</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6664585</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
